--- a/Piano HPC.xlsx
+++ b/Piano HPC.xlsx
@@ -3,12 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Schema Piano" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="dati" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="dati" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">HPC ENGINEERING 2024/25 - complete study plan composition</t>
   </si>
@@ -44,6 +43,12 @@
     <t>Crediti</t>
   </si>
   <si>
+    <t>Voto</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>MANDATORY</t>
   </si>
   <si>
@@ -83,27 +88,39 @@
     <t xml:space="preserve">QUANTUM COMPUTING</t>
   </si>
   <si>
+    <t xml:space="preserve">Electives AFFINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANTUM CIRCUITS AND DEVICES</t>
+  </si>
+  <si>
+    <t>Cambiare</t>
+  </si>
+  <si>
     <t>Electives</t>
   </si>
   <si>
-    <t xml:space="preserve">QUANTUM CIRCUITS AND DEVICES</t>
-  </si>
-  <si>
     <t xml:space="preserve">FONDAMENTI DI CALCOLO NUMERICO (obbligo)</t>
   </si>
   <si>
     <t xml:space="preserve">SCIENTIFIC COMPUTING TOOLS FOR ADVANCED MATHEMATICAL MODELLING</t>
   </si>
   <si>
-    <t xml:space="preserve">MATHEMATICAL MODELS AND METHODS FOR IMAGE PROCESSING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	COMPUTER SECURITY - UIC 587</t>
+    <t xml:space="preserve">Cambiare semestre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electives ICT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPUTER SECURITY - UIC 587</t>
   </si>
   <si>
     <t>ING-INF/04</t>
   </si>
   <si>
+    <t xml:space="preserve">PHOTONIC COMPUTING</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARTIFICIAL NEURAL NETWORKS AND DEEP LEARNING</t>
   </si>
   <si>
@@ -113,10 +130,16 @@
     <t xml:space="preserve">COMPUTER GRAPHICS</t>
   </si>
   <si>
+    <t xml:space="preserve">Electives APPLICATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH PERFORMANCE SCIENTIFIC COMPUTING IN AEROSPACE</t>
+  </si>
+  <si>
     <t>APPLICATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">HIGH PERFORMANCE SCIENTIFIC COMPUTING IN AEROSPACE</t>
+    <t xml:space="preserve">Aggiungere un altro applications</t>
   </si>
   <si>
     <t xml:space="preserve">THESIS / FINAL EXAM</t>
@@ -147,25 +170,13 @@
   </si>
   <si>
     <t xml:space="preserve">A SCELTA (IN QUALSIASI SETTORE)</t>
-  </si>
-  <si>
-    <t>Esame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 CFU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 CFU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 CFU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -243,12 +254,6 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11.000000"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9.000000"/>
       <color rgb="FF444444"/>
@@ -319,7 +324,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="33">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -358,6 +363,15 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -435,6 +449,19 @@
         <color auto="1"/>
       </right>
       <top style="none"/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color theme="0" tint="-0.14996795556505021"/>
       </bottom>
@@ -534,15 +561,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -686,93 +704,6 @@
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -787,7 +718,7 @@
     <xf fontId="5" fillId="5" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="81">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -811,285 +742,213 @@
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="6" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="10" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="11" fillId="8" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="11" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="11" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="11" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="11" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="11" fillId="8" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="8" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="11" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="11" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="11" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="7" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf fontId="2" fillId="2" borderId="12" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="13" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="13" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="3" borderId="10" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="3" borderId="12" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="11" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="3" borderId="13" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="11" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="3" borderId="13" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="12" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="2" borderId="10" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="11" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="11" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="12" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="13" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="14" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="15" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="3" borderId="13" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="3" fillId="3" borderId="14" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="14" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf fontId="4" fillId="4" borderId="15" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="15" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="4" borderId="16" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="4" borderId="16" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="4" borderId="0" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="17" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="4" borderId="14" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="15" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="2" borderId="16" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="16" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="17" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="9" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="7" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="12" fillId="7" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="12" fillId="7" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="12" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="7" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="7" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="11" fillId="7" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="8" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="13" fillId="8" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="8" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="13" fillId="8" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="7" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="13" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="10" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="7" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="14" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="13" fillId="7" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="10" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="15" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="14" fillId="7" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf fontId="16" fillId="7" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="10" fillId="7" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="7" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="16" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" vertical="center"/>
-    </xf>
-    <xf fontId="17" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="16" fillId="7" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="7" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="7" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="17" fillId="7" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="16" fillId="7" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="7" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="17" fillId="7" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="11" fillId="8" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="2" fillId="2" borderId="7" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="8" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="8" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="9" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="32" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="5" borderId="1" numFmtId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="33" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="34" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="11" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="11" fillId="7" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="5" borderId="36" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="5" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="7" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="11" fillId="7" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1119,11 +978,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
+      <xdr:colOff>236219</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>251460</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4389120" cy="9463360"/>
+    <xdr:ext cx="4389120" cy="9463359"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="CasellaDiTesto 1"/>
@@ -1131,8 +990,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9044940" y="251460"/>
-          <a:ext cx="4389120" cy="9463360"/>
+          <a:off x="9999344" y="251460"/>
+          <a:ext cx="4389120" cy="9463359"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1931,11 +1790,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>518159</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>441959</xdr:rowOff>
+      <xdr:colOff>518158</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>441958</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4389120" cy="421141"/>
+    <xdr:ext cx="4389120" cy="421140"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="CasellaDiTesto 2"/>
@@ -1943,8 +1802,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="518160" y="5943600"/>
-          <a:ext cx="4389120" cy="421141"/>
+          <a:off x="518158" y="6485571"/>
+          <a:ext cx="4389120" cy="421140"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2520,13 +2379,13 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="12.86328125"/>
+    <col customWidth="1" min="1" max="1" style="1" width="19.8515625"/>
     <col customWidth="1" min="2" max="2" style="2" width="11.19921875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="61.00390625"/>
+    <col customWidth="1" min="3" max="3" style="1" width="52.57421875"/>
     <col customWidth="1" min="4" max="4" style="1" width="18.19921875"/>
     <col customWidth="1" min="5" max="5" style="2" width="8.53125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" style="1" width="25.50390625"/>
-    <col min="7" max="7" style="1" width="9.1328125"/>
+    <col customWidth="1" min="6" max="6" style="1" width="6.8515625"/>
+    <col customWidth="1" min="7" max="7" style="1" width="27.140625"/>
     <col customWidth="1" min="8" max="8" style="1" width="49.1328125"/>
     <col min="9" max="16384" style="1" width="9.1328125"/>
   </cols>
@@ -2535,6 +2394,7 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" ht="15.75">
       <c r="A2" s="4" t="s">
@@ -2543,496 +2403,564 @@
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" s="6" customFormat="1">
       <c r="B3" s="7"/>
       <c r="E3" s="8"/>
-    </row>
-    <row r="4" s="9" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" s="10" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="H4" s="15"/>
+      <c r="F4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" ht="17.75" customHeight="1">
-      <c r="A5" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="A5" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="C5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="21">
+        <v>5</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
+    </row>
+    <row r="6" ht="17.75" customHeight="1">
+      <c r="A6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="20">
+      <c r="B6" s="25">
+        <v>1</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="27">
         <v>5</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6" ht="17.75" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="23">
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" s="28" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="30">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="C7" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="33">
+        <v>5</v>
+      </c>
+      <c r="F7" s="33">
+        <v>29</v>
+      </c>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+    </row>
+    <row r="8" ht="17.75" customHeight="1">
+      <c r="A8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="25">
+        <v>1</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="27">
+        <v>5</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" ht="17.75" customHeight="1">
+      <c r="A9" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="25">
+        <v>1</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="27">
+        <v>5</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A10" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="37">
+        <v>2</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E10" s="40">
         <v>5</v>
       </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" ht="17.75" customHeight="1">
-      <c r="A7" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="23">
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="35"/>
+    </row>
+    <row r="11" s="28" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="30">
+        <v>2</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="33">
+        <v>5</v>
+      </c>
+      <c r="F11" s="33">
+        <v>25</v>
+      </c>
+      <c r="G11" s="33"/>
+      <c r="H11" s="28"/>
+    </row>
+    <row r="12" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A12" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="37">
+        <v>2</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="40">
+        <v>5</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="35"/>
+    </row>
+    <row r="13" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A13" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="41">
+        <v>2</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="41">
+        <v>5</v>
+      </c>
+      <c r="F13" s="41"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="35"/>
+    </row>
+    <row r="14" s="28" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="30">
+        <v>2</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="33">
+        <v>5</v>
+      </c>
+      <c r="F14" s="33">
+        <v>23</v>
+      </c>
+      <c r="G14" s="33"/>
+      <c r="H14" s="28"/>
+    </row>
+    <row r="15" s="42" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A15" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="44">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C15" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="47">
+        <v>5</v>
+      </c>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="42"/>
+    </row>
+    <row r="16" s="28" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A16" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="50">
+        <v>2</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="52">
+        <v>5</v>
+      </c>
+      <c r="F16" s="52">
+        <v>24</v>
+      </c>
+      <c r="G16" s="33"/>
+      <c r="H16" s="28"/>
+    </row>
+    <row r="17" s="42" customFormat="1" ht="28.5">
+      <c r="A17" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="44">
+        <v>2</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="47">
+        <v>5</v>
+      </c>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="42"/>
+    </row>
+    <row r="18" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A18" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="41">
+        <v>2</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="41">
+        <v>5</v>
+      </c>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="53"/>
+    </row>
+    <row r="19" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A19" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="41">
+        <v>2</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="41">
+        <v>5</v>
+      </c>
+      <c r="F19" s="41"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" ht="17.75" customHeight="1">
+      <c r="A20" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="25">
+        <v>1</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E20" s="27">
         <v>5</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" ht="17.75" customHeight="1">
-      <c r="A8" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="23">
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+    </row>
+    <row r="21" s="0" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A21" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="25">
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="C21" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E21" s="27">
         <v>5</v>
       </c>
-      <c r="F8" s="25"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" ht="17.75" customHeight="1">
-      <c r="A9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="23">
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+    </row>
+    <row r="22" s="35" customFormat="1" ht="17.75" customHeight="1">
+      <c r="A22" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="41">
+        <v>2</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="41">
+        <v>5</v>
+      </c>
+      <c r="F22" s="41"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="35"/>
+    </row>
+    <row r="23" ht="17.75" customHeight="1">
+      <c r="A23" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="57">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="25">
-        <v>5</v>
-      </c>
-      <c r="F9" s="25"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" ht="17.75" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="C23" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="60">
+        <v>10</v>
+      </c>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="14.65">
+      <c r="A24" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="62">
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="25">
-        <v>5</v>
-      </c>
-      <c r="F10" s="25"/>
-    </row>
-    <row r="11" ht="17.75" customHeight="1">
-      <c r="A11" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23">
-        <v>2</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="25">
-        <v>5</v>
-      </c>
-      <c r="F11" s="25"/>
-    </row>
-    <row r="12" ht="17.75" customHeight="1">
-      <c r="A12" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="23">
-        <v>2</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="25">
-        <v>5</v>
-      </c>
-      <c r="F12" s="25"/>
-    </row>
-    <row r="13" s="26" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="28">
-        <v>2</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="31">
-        <v>5</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="H13" s="26"/>
-    </row>
-    <row r="14" s="32" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A14" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="34">
-        <v>2</v>
-      </c>
-      <c r="C14" s="35" t="s">
+      <c r="C24" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="65">
         <v>20</v>
       </c>
-      <c r="D14" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="37">
-        <v>5</v>
-      </c>
-      <c r="F14" s="37">
-        <v>23</v>
-      </c>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" ht="17.75" customHeight="1">
-      <c r="A15" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="39">
-        <v>1</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="42">
-        <v>5</v>
-      </c>
-      <c r="F15" s="42"/>
-    </row>
-    <row r="16" s="32" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A16" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="44">
-        <v>2</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="46">
-        <v>5</v>
-      </c>
-      <c r="F16" s="46">
-        <v>24</v>
-      </c>
-      <c r="H16" s="32"/>
-    </row>
-    <row r="17" ht="17.75" customHeight="1">
-      <c r="A17" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="39">
-        <v>2</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="42">
-        <v>5</v>
-      </c>
-      <c r="F17" s="42"/>
-    </row>
-    <row r="18" s="0" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A18" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="48">
-        <v>2</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="48">
-        <v>5</v>
-      </c>
-      <c r="F18" s="49"/>
-      <c r="H18"/>
-    </row>
-    <row r="19" s="50" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A19" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="48">
-        <v>2</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="48">
-        <v>5</v>
-      </c>
-      <c r="F19" s="48"/>
-      <c r="H19" s="50"/>
-    </row>
-    <row r="20" ht="17.75" customHeight="1">
-      <c r="A20" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="23">
-        <v>1</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="25">
-        <v>5</v>
-      </c>
-      <c r="F20" s="25"/>
-    </row>
-    <row r="21" ht="17.75" customHeight="1">
-      <c r="A21" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="23">
-        <v>1</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="25">
-        <v>5</v>
-      </c>
-      <c r="F21" s="25"/>
-    </row>
-    <row r="22" s="26" customFormat="1" ht="17.75" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="52">
-        <v>2</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="54">
-        <v>5</v>
-      </c>
-      <c r="F22" s="54"/>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" ht="17.75" customHeight="1">
-      <c r="A23" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="56">
-        <v>1</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="59">
-        <v>10</v>
-      </c>
-      <c r="F23" s="59"/>
-    </row>
-    <row r="24" ht="17.75" customHeight="1">
-      <c r="A24" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="61">
-        <v>2</v>
-      </c>
-      <c r="C24" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="64">
-        <v>20</v>
-      </c>
-      <c r="F24" s="64"/>
-    </row>
-    <row r="25" ht="14.65"/>
-    <row r="26" s="6" customFormat="1" ht="20.75" customHeight="1">
+      <c r="F24" s="65"/>
+      <c r="G24" s="66"/>
+    </row>
+    <row r="25" s="6" customFormat="1" ht="20.75" customHeight="1">
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="B26" s="8"/>
-      <c r="D26" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="66"/>
-    </row>
-    <row r="27" s="6" customFormat="1" ht="19.5" customHeight="1">
+      <c r="D26" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="68"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" s="6" customFormat="1" ht="38.25" customHeight="1">
       <c r="B27" s="8"/>
-      <c r="D27" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="68">
+      <c r="D27" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="70">
         <f>SUM(E5:E24)</f>
         <v>120</v>
       </c>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" s="6" customFormat="1" ht="38.25" customHeight="1">
       <c r="B28" s="8"/>
-      <c r="C28" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="71">
+      <c r="C28" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="73">
         <f>SUMIF(D5:D24,"ING-INF/05 - INFO",E5:E24)+SUMIF(D5:D24,"ING-INF/04",E5:E24)</f>
         <v>45</v>
       </c>
-      <c r="F28" s="72" t="s">
-        <v>39</v>
+      <c r="F28" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="74" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" s="6" customFormat="1" ht="38.25" customHeight="1">
       <c r="B29" s="8"/>
-      <c r="D29" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="74">
+      <c r="D29" s="75" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="76">
         <f>SUMIF(D5:D24,"AFFINI",E5:E24)</f>
-        <v>40</v>
-      </c>
-      <c r="F29" s="72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" s="6" customFormat="1" ht="38.25" customHeight="1">
+        <v>45</v>
+      </c>
+      <c r="F29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" s="6" customFormat="1" ht="23.75" customHeight="1">
       <c r="B30" s="8"/>
-      <c r="D30" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="76">
+      <c r="D30" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="78">
         <f>SUMIF(D5:D24,"APPLICATIONS",E5:E24)</f>
-        <v>15</v>
-      </c>
-      <c r="F30" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75">
+      <c r="B31" s="8"/>
+      <c r="D31" s="79" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" s="6" customFormat="1" ht="23.75" customHeight="1">
-      <c r="B31" s="8"/>
-      <c r="D31" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="78">
+      <c r="E31" s="80">
         <f>SUMIF(D5:D24,"THESIS",E5:E24)</f>
         <v>20</v>
       </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="E32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D26:E26"/>
   </mergeCells>
-  <dataValidations count="1" disablePrompts="0">
-    <dataValidation sqref="D5:D24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+  <dataValidations count="4" disablePrompts="0">
+    <dataValidation sqref="D5:D17 D20:D21 D23:D24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <formula1>dati!$A$1:$A$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="D22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <formula1>dati!$A$1:$A$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="D19" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <formula1>dati!$A$1:$A$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="D18" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>dati!$A$1:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="C19" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="between" id="{008E008E-00EF-4B22-BDC6-00F100D900AD}">
+          <x14:cfRule type="cellIs" priority="13" operator="between" id="{00DF000C-0005-477F-A65B-009900CB0073}">
             <xm:f>45</xm:f>
             <xm:f>65</xm:f>
             <x14:dxf>
@@ -3050,7 +2978,7 @@
           <xm:sqref>E28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="12" operator="between" id="{00480071-006E-49DF-A6D5-005100FA0028}">
+          <x14:cfRule type="cellIs" priority="12" operator="between" id="{00DD0095-0047-4B8C-B7B0-00FC00E3009F}">
             <xm:f>30</xm:f>
             <xm:f>45</xm:f>
             <x14:dxf>
@@ -3068,7 +2996,7 @@
           <xm:sqref>E29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="11" operator="between" id="{006F009B-0006-4B4A-87A9-007200F80051}">
+          <x14:cfRule type="cellIs" priority="11" operator="between" id="{00C20001-0049-40FE-BE39-006A00EF0061}">
             <xm:f>10</xm:f>
             <xm:f>20</xm:f>
             <x14:dxf>
@@ -3086,7 +3014,7 @@
           <xm:sqref>E30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{005400C8-00F9-4378-ADB5-00AB0089006A}">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00E1000C-00F7-4B09-B066-0092008800AF}">
             <xm:f>45</xm:f>
             <x14:dxf>
               <font>
@@ -3103,7 +3031,7 @@
           <xm:sqref>E28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{00600053-00FF-4B01-9A4B-00B8009A00F9}">
+          <x14:cfRule type="cellIs" priority="9" operator="greaterThan" id="{002F00E3-00C2-4BB1-B509-0059008D0015}">
             <xm:f>65</xm:f>
             <x14:dxf>
               <font>
@@ -3120,7 +3048,7 @@
           <xm:sqref>E28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" operator="lessThan" id="{008D00C0-00C0-4583-9B0B-003800CC004A}">
+          <x14:cfRule type="cellIs" priority="8" operator="lessThan" id="{00C600A9-0020-4C4E-A5DE-005700A20032}">
             <xm:f>30</xm:f>
             <x14:dxf>
               <font>
@@ -3137,7 +3065,7 @@
           <xm:sqref>E29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="greaterThan" id="{00EB0033-005A-481D-B267-003000F200EA}">
+          <x14:cfRule type="cellIs" priority="7" operator="greaterThan" id="{006200F3-0008-460F-A1FC-005800AC003A}">
             <xm:f>45</xm:f>
             <x14:dxf>
               <font>
@@ -3154,7 +3082,7 @@
           <xm:sqref>E29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="lessThan" id="{001C00F6-00E1-4FF5-902C-00870094002D}">
+          <x14:cfRule type="cellIs" priority="6" operator="lessThan" id="{00E7004C-0077-4A74-B066-00DC00570072}">
             <xm:f>10</xm:f>
             <x14:dxf>
               <font>
@@ -3171,7 +3099,7 @@
           <xm:sqref>E30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="greaterThan" id="{00D800F7-00DA-48B3-99F5-0088006F00AA}">
+          <x14:cfRule type="cellIs" priority="5" operator="greaterThan" id="{00D900B1-00ED-4BD3-B27D-0097009000B7}">
             <xm:f>20</xm:f>
             <x14:dxf>
               <font>
@@ -3188,7 +3116,7 @@
           <xm:sqref>E30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{006A0047-00BF-4303-83B4-006300F200BA}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{00E20016-00F0-45D4-A689-00F1000B00F7}">
             <xm:f>120</xm:f>
             <x14:dxf>
               <font>
@@ -3205,7 +3133,7 @@
           <xm:sqref>E27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{0031009C-007E-4B16-B82F-00AC00C200FC}">
+          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{005000E0-0088-45F4-BA39-008800BE00B6}">
             <xm:f>120</xm:f>
             <x14:dxf>
               <font>
@@ -3222,7 +3150,7 @@
           <xm:sqref>E27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThan" id="{002000D0-00FA-4F21-917E-00DA003700D4}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThan" id="{00940068-00C2-4406-AD18-00A90064008B}">
             <xm:f>120</xm:f>
             <x14:dxf>
               <font>
@@ -3239,7 +3167,7 @@
           <xm:sqref>E27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{003E0060-0088-45DD-A18D-00C900DD00E7}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{00C5007F-002E-4AAD-831C-00DB00FC00A1}">
             <xm:f>20</xm:f>
             <x14:dxf>
               <font>
@@ -3264,559 +3192,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col bestFit="1" min="1" max="1" width="12.07421875"/>
-    <col customWidth="1" min="3" max="3" width="64.00390625"/>
-    <col bestFit="1" min="4" max="4" width="16.07421875"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="79" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="80"/>
-      <c r="I2" s="81"/>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="82" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="83">
-        <v>2</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="86">
-        <v>5</v>
-      </c>
-      <c r="F3" s="87">
-        <v>23</v>
-      </c>
-      <c r="G3" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="89">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="90">
-        <v>2</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="46">
-        <v>5</v>
-      </c>
-      <c r="F4" s="91">
-        <v>24</v>
-      </c>
-      <c r="G4" s="88"/>
-      <c r="H4" s="92"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="H5" s="92"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="17">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="20">
-        <v>5</v>
-      </c>
-      <c r="F6" s="93"/>
-      <c r="G6" s="88" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="92"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="23">
-        <v>1</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="25">
-        <v>5</v>
-      </c>
-      <c r="F7" s="94"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="92"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="23">
-        <v>1</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="25">
-        <v>5</v>
-      </c>
-      <c r="F8" s="94"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="92"/>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="23">
-        <v>1</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="25">
-        <v>5</v>
-      </c>
-      <c r="F9" s="94"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="92"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="23">
-        <v>1</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="25">
-        <v>5</v>
-      </c>
-      <c r="F10" s="94"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="92"/>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="H11" s="92"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="49">
-        <v>2</v>
-      </c>
-      <c r="C12" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="49">
-        <v>5</v>
-      </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="95" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="92"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="49">
-        <v>2</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="49">
-        <v>5</v>
-      </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="92"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="49">
-        <v>2</v>
-      </c>
-      <c r="C14" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="49">
-        <v>5</v>
-      </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="92"/>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="49">
-        <v>2</v>
-      </c>
-      <c r="C15" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="49">
-        <v>5</v>
-      </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="92"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="97">
-        <v>2</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="97">
-        <v>5</v>
-      </c>
-      <c r="F16" s="49"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="92"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="48">
-        <v>2</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="48">
-        <v>5</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="92"/>
-    </row>
-    <row r="18" ht="14.25"/>
-    <row r="19" ht="14.25">
-      <c r="A19" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="23">
-        <v>1</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="25">
-        <v>5</v>
-      </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="88">
-        <v>25</v>
-      </c>
-      <c r="H19" s="98">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="23">
-        <v>1</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="25">
-        <v>5</v>
-      </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="98"/>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="56">
-        <v>1</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="59">
-        <v>10</v>
-      </c>
-      <c r="F21" s="99"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="98"/>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="100">
-        <v>1</v>
-      </c>
-      <c r="C22" s="101" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="42">
-        <v>5</v>
-      </c>
-      <c r="F22" s="102"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="98"/>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="101"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="98"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="48">
-        <v>2</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="48">
-        <v>5</v>
-      </c>
-      <c r="F24" s="49"/>
-      <c r="G24" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="98"/>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="39">
-        <v>2</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="42">
-        <v>5</v>
-      </c>
-      <c r="G25" s="88"/>
-      <c r="H25" s="98"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="61">
-        <v>2</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="64">
-        <v>20</v>
-      </c>
-      <c r="F26" s="104"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="98"/>
-    </row>
-    <row r="27" ht="14.25"/>
-    <row r="28" ht="14.25"/>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H17"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="G12:G17"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H26"/>
-    <mergeCell ref="G24:G26"/>
-  </mergeCells>
-  <dataValidations count="12" disablePrompts="0">
-    <dataValidation sqref="D2" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D4" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D6:D10" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D12:D15" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D25" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D16" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D19:D20" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D21" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D26" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="D17" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>dati!$A$1:$A$5</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
